--- a/src/templates/import/Printer.xlsx
+++ b/src/templates/import/Printer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ITAMS\itams-system\src\templates\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app-infra\src\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BD2289-7E29-49A7-9E17-ED38F79CDFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01180DB0-F676-4CAC-A3A5-335183E27761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="87">
   <si>
     <t>Barcode</t>
   </si>
@@ -34,7 +34,7 @@
   </si>
   <si>
     <t>CHRIS ROOM</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HP Color Laser MFP 178nw</t>
@@ -47,7 +47,7 @@
   </si>
   <si>
     <t>10.1.34.210</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/1F/FC</t>
@@ -60,14 +60,14 @@
   </si>
   <si>
     <t>Share Printer</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/2F/FB</t>
   </si>
   <si>
     <t>FCM</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HP COLOR LASERJET PRO MFP M176N</t>
@@ -77,7 +77,7 @@
   </si>
   <si>
     <t>HR</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON L360</t>
@@ -87,26 +87,26 @@
   </si>
   <si>
     <t>PUR-PRO</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HP LASERJET PRO MFP M227fdw</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Z012060010020003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/1F/FB</t>
   </si>
   <si>
     <t>HP Designjet t520 36in</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>10.1.34.167</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/1F/TECH</t>
@@ -119,39 +119,39 @@
   </si>
   <si>
     <t>PRO-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HP LASERJET PRO 4003dn</t>
   </si>
   <si>
     <t>10.1.34.169</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/XC/OFFICE</t>
   </si>
   <si>
     <t>PRO-2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON M2140</t>
   </si>
   <si>
     <t>Office 4/2F/inlogo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PRO-5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON L310</t>
   </si>
   <si>
     <t>PMQA</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON L3210</t>
@@ -161,63 +161,63 @@
   </si>
   <si>
     <t>IT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Z012060640010001</t>
   </si>
   <si>
     <t>COSTING/BOM</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON L3210</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/2F/FB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">HP OFFICEJET 7612 WIDE FORMATE </t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Z012060190020002</t>
   </si>
   <si>
     <t>SHIP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON LQ590</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Z012060230000002</t>
   </si>
   <si>
     <t>EPSON L310</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>QC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HP LASERJET PRO M402dn</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CANON MF249du Multifunction Laser</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Z012060600010006</t>
   </si>
   <si>
     <t>PLAN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Z012060010020004</t>
@@ -227,15 +227,15 @@
   </si>
   <si>
     <t>DEV</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/1F/FB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SOP/SAMPLE/TECH-PRO</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON LQ2190</t>
@@ -254,54 +254,51 @@
   </si>
   <si>
     <t>WH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON LQ2090</t>
   </si>
   <si>
     <t>OFFICE/1F/FA</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EPSON LQ590</t>
   </si>
   <si>
     <t>SQ</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>OFFICE/1F/FC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TCS MH241 PRINTER 203DL</t>
   </si>
   <si>
     <t>10.1.34.130</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>LASER JEST PRO 4003dn</t>
   </si>
   <si>
     <t>10.1.34.131</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TECH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>RUBBER</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">                         INVENTORY PRINTER INFORMATION DAIHOA 06/2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Dept</t>
@@ -338,7 +335,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_);\(0\)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,14 +344,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -400,21 +389,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -437,26 +417,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -751,74 +726,88 @@
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="24.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="32.25" customHeight="1">
+    <row r="2" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>87</v>
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="G3" s="2">
+        <v>900000000610</v>
       </c>
       <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" ht="32.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -827,22 +816,23 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2">
-        <v>900000000610</v>
+        <v>900000000974</v>
       </c>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="32.25" customHeight="1">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" ht="25.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
@@ -851,82 +841,85 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>87</v>
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2">
-        <v>900000000974</v>
+        <v>900000000986</v>
       </c>
       <c r="H5" s="3"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="25.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>87</v>
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="2">
-        <v>900000000986</v>
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H6" s="3"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="25.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>87</v>
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="3"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>87</v>
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>5</v>
@@ -935,69 +928,72 @@
         <v>5</v>
       </c>
       <c r="H8" s="3"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="25.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>87</v>
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>5</v>
+      <c r="G9" s="2">
+        <v>900000001729</v>
       </c>
       <c r="H9" s="3"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>86</v>
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="2">
-        <v>900000001729</v>
+      <c r="G10" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H10" s="3"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="25.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1007,78 +1003,82 @@
         <v>5</v>
       </c>
       <c r="H11" s="3"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="25.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>87</v>
+        <v>37</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>5</v>
+      <c r="G12" s="2">
+        <v>900000001728</v>
       </c>
       <c r="H12" s="3"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" ht="25.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>87</v>
+        <v>16</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G13" s="2">
-        <v>900000001728</v>
+        <v>900000000985</v>
       </c>
       <c r="H13" s="3"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="25.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>87</v>
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2">
-        <v>900000000985</v>
+        <v>900000001278</v>
       </c>
       <c r="H14" s="3"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" ht="25.5" customHeight="1">
       <c r="A15" s="1" t="s">
@@ -1091,22 +1091,23 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>87</v>
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G15" s="2">
-        <v>900000001278</v>
+        <v>900000001420</v>
       </c>
       <c r="H15" s="3"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" ht="25.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -1115,20 +1116,21 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>87</v>
+        <v>47</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G16" s="2">
-        <v>900000001420</v>
+        <v>900000000609</v>
       </c>
       <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="25.5" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1139,44 +1141,46 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="2">
-        <v>900000000609</v>
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="25.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>87</v>
+        <v>51</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>5</v>
+      <c r="G18" s="2">
+        <v>900000001502</v>
       </c>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="25.5" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1187,20 +1191,21 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G19" s="2">
-        <v>900000001502</v>
+        <v>900000001730</v>
       </c>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="25.5" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
@@ -1213,18 +1218,19 @@
       <c r="D20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>87</v>
+      <c r="E20" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="2">
-        <v>900000001730</v>
+      <c r="G20" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="25.5" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>50</v>
       </c>
@@ -1235,20 +1241,21 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>87</v>
+        <v>52</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>5</v>
+      <c r="G21" s="2">
+        <v>900000001286</v>
       </c>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" ht="25.5" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>50</v>
       </c>
@@ -1259,20 +1266,21 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2">
-        <v>900000001286</v>
+        <v>900000001231</v>
       </c>
       <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" ht="25.5" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -1285,42 +1293,44 @@
       <c r="D23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>87</v>
+      <c r="E23" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="2">
-        <v>900000001231</v>
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" ht="25.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>87</v>
+        <v>19</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>5</v>
+        <v>55</v>
+      </c>
+      <c r="G24" s="2">
+        <v>900000001418</v>
       </c>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" ht="25.5" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -1331,34 +1341,35 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="2">
-        <v>900000001418</v>
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" ht="25.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>87</v>
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>5</v>
@@ -1367,8 +1378,9 @@
         <v>5</v>
       </c>
       <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" ht="25.5" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>57</v>
       </c>
@@ -1379,22 +1391,23 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>87</v>
+        <v>35</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>5</v>
+      <c r="G27" s="2">
+        <v>900000001132</v>
       </c>
       <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" ht="25.5" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>58</v>
@@ -1403,20 +1416,21 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>87</v>
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2">
-        <v>900000001132</v>
+        <v>61</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" ht="25.5" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>59</v>
       </c>
@@ -1427,20 +1441,21 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>86</v>
+        <v>62</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" ht="25.5" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1451,20 +1466,21 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>86</v>
+        <v>64</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" ht="25.5" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>59</v>
       </c>
@@ -1475,9 +1491,9 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F31" s="2" t="s">
@@ -1487,8 +1503,9 @@
         <v>5</v>
       </c>
       <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" ht="25.5" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
@@ -1499,44 +1516,46 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>87</v>
+        <v>37</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>5</v>
+      <c r="G32" s="2">
+        <v>900000001731</v>
       </c>
       <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" ht="25.5" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>87</v>
+        <v>66</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="2">
-        <v>900000001731</v>
+      <c r="G33" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" ht="25.5" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>65</v>
       </c>
@@ -1549,18 +1568,19 @@
       <c r="D34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>86</v>
+      <c r="E34" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>5</v>
+      <c r="G34" s="2">
+        <v>900000000563</v>
       </c>
       <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9" ht="25.5" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>65</v>
       </c>
@@ -1571,44 +1591,46 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>86</v>
+        <v>68</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="2">
-        <v>900000000563</v>
+        <v>900000000608</v>
       </c>
       <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" ht="25.5" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>86</v>
+        <v>28</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G36" s="2">
-        <v>900000000608</v>
+      <c r="G36" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9" ht="25.5" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>69</v>
       </c>
@@ -1619,10 +1641,10 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>86</v>
+        <v>60</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>5</v>
@@ -1631,8 +1653,9 @@
         <v>5</v>
       </c>
       <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9" ht="25.5" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>69</v>
       </c>
@@ -1645,8 +1668,8 @@
       <c r="D38" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>86</v>
+      <c r="E38" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -1655,8 +1678,9 @@
         <v>5</v>
       </c>
       <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9" ht="25.5" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>69</v>
       </c>
@@ -1669,8 +1693,8 @@
       <c r="D39" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>86</v>
+      <c r="E39" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>5</v>
@@ -1679,8 +1703,9 @@
         <v>5</v>
       </c>
       <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" ht="25.5" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>69</v>
       </c>
@@ -1693,8 +1718,8 @@
       <c r="D40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>86</v>
+      <c r="E40" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>5</v>
@@ -1703,8 +1728,9 @@
         <v>5</v>
       </c>
       <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" ht="25.5" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -1712,23 +1738,24 @@
         <v>70</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>86</v>
+        <v>71</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>5</v>
+      <c r="G41" s="2">
+        <v>514000000251</v>
       </c>
       <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" ht="25.5" customHeight="1">
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" ht="25.5" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>69</v>
       </c>
@@ -1736,51 +1763,25 @@
         <v>70</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>86</v>
+        <v>73</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="2">
-        <v>514000000251</v>
+      <c r="G42" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3"/>
+      <c r="I42" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/templates/import/Printer.xlsx
+++ b/src/templates/import/Printer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app-infra\src\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01180DB0-F676-4CAC-A3A5-335183E27761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CEA67A-6982-4167-8798-3BCC2AEE2FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="85">
   <si>
     <t>Barcode</t>
   </si>
@@ -40,292 +40,286 @@
     <t>HP Color Laser MFP 178nw</t>
   </si>
   <si>
-    <t>No barcode</t>
+    <t>10.1.34.210</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/1F/FC</t>
+  </si>
+  <si>
+    <t>EPSON LQ2190Q</t>
+  </si>
+  <si>
+    <t>Z012060420010005</t>
+  </si>
+  <si>
+    <t>Share Printer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/2F/FB</t>
+  </si>
+  <si>
+    <t>FCM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP COLOR LASERJET PRO MFP M176N</t>
+  </si>
+  <si>
+    <t>Z012060590010001</t>
+  </si>
+  <si>
+    <t>HR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON L360</t>
+  </si>
+  <si>
+    <t>Z012060640010002</t>
+  </si>
+  <si>
+    <t>PUR-PRO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP LASERJET PRO MFP M227fdw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z012060010020003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/1F/FB</t>
+  </si>
+  <si>
+    <t>HP Designjet t520 36in</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.1.34.167</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/1F/TECH</t>
+  </si>
+  <si>
+    <t>EPSON L3110</t>
+  </si>
+  <si>
+    <t>OFFICE/1F/RUB</t>
+  </si>
+  <si>
+    <t>PRO-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP LASERJET PRO 4003dn</t>
+  </si>
+  <si>
+    <t>10.1.34.169</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/XC/OFFICE</t>
+  </si>
+  <si>
+    <t>PRO-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON M2140</t>
+  </si>
+  <si>
+    <t>Office 4/2F/inlogo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRO-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON L310</t>
+  </si>
+  <si>
+    <t>PMQA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON L3210</t>
+  </si>
+  <si>
+    <t>OFFICE/XA/PMQA</t>
+  </si>
+  <si>
+    <t>IT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z012060640010001</t>
+  </si>
+  <si>
+    <t>COSTING/BOM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON L3210</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/2F/FB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HP OFFICEJET 7612 WIDE FORMATE </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z012060190020002</t>
+  </si>
+  <si>
+    <t>SHIP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON LQ590</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z012060230000002</t>
+  </si>
+  <si>
+    <t>EPSON L310</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP LASERJET PRO M402dn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CANON MF249du Multifunction Laser</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z012060600010006</t>
+  </si>
+  <si>
+    <t>PLAN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z012060010020004</t>
+  </si>
+  <si>
+    <t>HP COLOR LASER MFP 178nw</t>
+  </si>
+  <si>
+    <t>DEV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/1F/FB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP/SAMPLE/TECH-PRO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON LQ2190</t>
+  </si>
+  <si>
+    <t>Z012060420010004</t>
+  </si>
+  <si>
+    <t>HP LASERJETPRO 400 M401n</t>
+  </si>
+  <si>
+    <t>Z012060460010001</t>
+  </si>
+  <si>
+    <t>HP LASERJET PRO MFP M227fdw</t>
+  </si>
+  <si>
+    <t>WH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON LQ2090</t>
+  </si>
+  <si>
+    <t>OFFICE/1F/FA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPSON LQ590</t>
+  </si>
+  <si>
+    <t>SQ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFICE/1F/FC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCS MH241 PRINTER 203DL</t>
+  </si>
+  <si>
+    <t>10.1.34.130</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LASER JEST PRO 4003dn</t>
+  </si>
+  <si>
+    <t>10.1.34.131</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TECH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RUBBER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dept</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>SAP_code</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
   <si>
     <t>No Barcode</t>
   </si>
   <si>
-    <t>10.1.34.210</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/1F/FC</t>
-  </si>
-  <si>
-    <t>EPSON LQ2190Q</t>
-  </si>
-  <si>
-    <t>Z012060420010005</t>
-  </si>
-  <si>
-    <t>Share Printer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/2F/FB</t>
-  </si>
-  <si>
-    <t>FCM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP COLOR LASERJET PRO MFP M176N</t>
-  </si>
-  <si>
-    <t>Z012060590010001</t>
-  </si>
-  <si>
-    <t>HR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON L360</t>
-  </si>
-  <si>
-    <t>Z012060640010002</t>
-  </si>
-  <si>
-    <t>PUR-PRO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP LASERJET PRO MFP M227fdw</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z012060010020003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/1F/FB</t>
-  </si>
-  <si>
-    <t>HP Designjet t520 36in</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.1.34.167</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/1F/TECH</t>
-  </si>
-  <si>
-    <t>EPSON L3110</t>
-  </si>
-  <si>
-    <t>OFFICE/1F/RUB</t>
-  </si>
-  <si>
-    <t>PRO-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP LASERJET PRO 4003dn</t>
-  </si>
-  <si>
-    <t>10.1.34.169</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/XC/OFFICE</t>
-  </si>
-  <si>
-    <t>PRO-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON M2140</t>
-  </si>
-  <si>
-    <t>Office 4/2F/inlogo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRO-5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON L310</t>
-  </si>
-  <si>
-    <t>PMQA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON L3210</t>
-  </si>
-  <si>
-    <t>OFFICE/XA/PMQA</t>
-  </si>
-  <si>
-    <t>IT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z012060640010001</t>
-  </si>
-  <si>
-    <t>COSTING/BOM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON L3210</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/2F/FB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">HP OFFICEJET 7612 WIDE FORMATE </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z012060190020002</t>
-  </si>
-  <si>
-    <t>SHIP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON LQ590</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z012060230000002</t>
-  </si>
-  <si>
-    <t>EPSON L310</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>QC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP LASERJET PRO M402dn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CANON MF249du Multifunction Laser</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z012060600010006</t>
-  </si>
-  <si>
-    <t>PLAN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z012060010020004</t>
-  </si>
-  <si>
-    <t>HP COLOR LASER MFP 178nw</t>
-  </si>
-  <si>
-    <t>DEV</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/1F/FB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOP/SAMPLE/TECH-PRO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON LQ2190</t>
-  </si>
-  <si>
-    <t>Z012060420010004</t>
-  </si>
-  <si>
-    <t>HP LASERJETPRO 400 M401n</t>
-  </si>
-  <si>
-    <t>Z012060460010001</t>
-  </si>
-  <si>
-    <t>HP LASERJET PRO MFP M227fdw</t>
-  </si>
-  <si>
-    <t>WH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON LQ2090</t>
-  </si>
-  <si>
-    <t>OFFICE/1F/FA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EPSON LQ590</t>
-  </si>
-  <si>
-    <t>SQ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFICE/1F/FC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TCS MH241 PRINTER 203DL</t>
-  </si>
-  <si>
-    <t>10.1.34.130</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LASER JEST PRO 4003dn</t>
-  </si>
-  <si>
-    <t>10.1.34.131</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TECH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RUBBER</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dept</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
-    <t>SAP_code</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>YES</t>
+    <t>Black &amp; White</t>
   </si>
 </sst>
 </file>
@@ -728,28 +722,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24.75" customHeight="1">
       <c r="A1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>1</v>
@@ -760,44 +754,44 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2">
         <v>900000000610</v>
@@ -807,22 +801,22 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="2">
         <v>900000000974</v>
@@ -832,22 +826,22 @@
     </row>
     <row r="5" spans="1:9" ht="25.5" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="2">
         <v>900000000986</v>
@@ -857,97 +851,97 @@
     </row>
     <row r="6" spans="1:9" ht="25.5" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="25.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="25.5" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2">
         <v>900000001729</v>
@@ -957,72 +951,72 @@
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="25.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="25.5" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2">
         <v>900000001728</v>
@@ -1032,22 +1026,22 @@
     </row>
     <row r="13" spans="1:9" ht="25.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2">
         <v>900000000985</v>
@@ -1057,22 +1051,22 @@
     </row>
     <row r="14" spans="1:9" ht="25.5" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2">
         <v>900000001278</v>
@@ -1082,22 +1076,22 @@
     </row>
     <row r="15" spans="1:9" ht="25.5" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="G15" s="2">
         <v>900000001420</v>
@@ -1107,22 +1101,22 @@
     </row>
     <row r="16" spans="1:9" ht="25.5" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G16" s="2">
         <v>900000000609</v>
@@ -1132,47 +1126,47 @@
     </row>
     <row r="17" spans="1:9" ht="25.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="25.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2">
         <v>900000001502</v>
@@ -1182,22 +1176,22 @@
     </row>
     <row r="19" spans="1:9" ht="25.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2">
         <v>900000001730</v>
@@ -1207,47 +1201,47 @@
     </row>
     <row r="20" spans="1:9" ht="25.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" ht="25.5" customHeight="1">
       <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2">
         <v>900000001286</v>
@@ -1257,22 +1251,22 @@
     </row>
     <row r="22" spans="1:9" ht="25.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="2">
         <v>900000001231</v>
@@ -1282,47 +1276,47 @@
     </row>
     <row r="23" spans="1:9" ht="25.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="25.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2">
         <v>900000001418</v>
@@ -1332,72 +1326,72 @@
     </row>
     <row r="25" spans="1:9" ht="25.5" customHeight="1">
       <c r="A25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" ht="25.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" ht="25.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2">
         <v>900000001132</v>
@@ -1407,122 +1401,122 @@
     </row>
     <row r="28" spans="1:9" ht="25.5" customHeight="1">
       <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="G28" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" ht="25.5" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" ht="25.5" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" ht="25.5" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" ht="25.5" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G32" s="2">
         <v>900000001731</v>
@@ -1532,47 +1526,47 @@
     </row>
     <row r="33" spans="1:9" ht="25.5" customHeight="1">
       <c r="A33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="25.5" customHeight="1">
       <c r="A34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G34" s="2">
         <v>900000000563</v>
@@ -1582,22 +1576,22 @@
     </row>
     <row r="35" spans="1:9" ht="25.5" customHeight="1">
       <c r="A35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G35" s="2">
         <v>900000000608</v>
@@ -1607,147 +1601,147 @@
     </row>
     <row r="36" spans="1:9" ht="25.5" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" ht="25.5" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" ht="25.5" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" ht="25.5" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="25.5" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:9" ht="25.5" customHeight="1">
       <c r="A41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G41" s="2">
         <v>514000000251</v>
@@ -1757,25 +1751,25 @@
     </row>
     <row r="42" spans="1:9" ht="25.5" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="5"/>

--- a/src/templates/import/Printer.xlsx
+++ b/src/templates/import/Printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app-infra\src\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CEA67A-6982-4167-8798-3BCC2AEE2FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C09F368-44B6-4092-836F-009FE950232C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,9 +310,6 @@
     <t>Color</t>
   </si>
   <si>
-    <t>SAP_code</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>Black &amp; White</t>
+  </si>
+  <si>
+    <t>SAPCode</t>
   </si>
 </sst>
 </file>
@@ -740,10 +740,10 @@
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>1</v>
@@ -766,10 +766,10 @@
         <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="5"/>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -869,7 +869,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5"/>
@@ -891,10 +891,10 @@
         <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="5"/>
@@ -916,10 +916,10 @@
         <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="5"/>
@@ -938,10 +938,10 @@
         <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2">
         <v>900000001729</v>
@@ -963,13 +963,13 @@
         <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="5"/>
@@ -991,10 +991,10 @@
         <v>80</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="5"/>
@@ -1016,7 +1016,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2">
         <v>900000001728</v>
@@ -1066,7 +1066,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2">
         <v>900000001278</v>
@@ -1113,7 +1113,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>46</v>
@@ -1141,10 +1141,10 @@
         <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="5"/>
@@ -1163,10 +1163,10 @@
         <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2">
         <v>900000001502</v>
@@ -1191,7 +1191,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2">
         <v>900000001730</v>
@@ -1216,10 +1216,10 @@
         <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
@@ -1238,10 +1238,10 @@
         <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2">
         <v>900000001286</v>
@@ -1291,10 +1291,10 @@
         <v>80</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
@@ -1313,7 +1313,7 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>53</v>
@@ -1341,10 +1341,10 @@
         <v>80</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="5"/>
@@ -1366,10 +1366,10 @@
         <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="5"/>
@@ -1391,7 +1391,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2">
         <v>900000001132</v>
@@ -1413,13 +1413,13 @@
         <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>59</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="5"/>
@@ -1438,13 +1438,13 @@
         <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="5"/>
@@ -1463,13 +1463,13 @@
         <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="5"/>
@@ -1491,10 +1491,10 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="5"/>
@@ -1516,7 +1516,7 @@
         <v>80</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G32" s="2">
         <v>900000001731</v>
@@ -1538,13 +1538,13 @@
         <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="5"/>
@@ -1563,10 +1563,10 @@
         <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G34" s="2">
         <v>900000000563</v>
@@ -1588,10 +1588,10 @@
         <v>66</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G35" s="2">
         <v>900000000608</v>
@@ -1613,13 +1613,13 @@
         <v>26</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="5"/>
@@ -1638,13 +1638,13 @@
         <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="5"/>
@@ -1663,13 +1663,13 @@
         <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="5"/>
@@ -1688,13 +1688,13 @@
         <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="5"/>
@@ -1713,13 +1713,13 @@
         <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="5"/>
@@ -1738,10 +1738,10 @@
         <v>69</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G41" s="2">
         <v>514000000251</v>
@@ -1763,13 +1763,13 @@
         <v>71</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="5"/>
